--- a/TITAN-STAR-維修記錄模板.xlsx
+++ b/TITAN-STAR-維修記錄模板.xlsx
@@ -5,9 +5,10 @@
   <sheets>
     <sheet name="機種清冊" sheetId="1" r:id="rId1"/>
     <sheet name="維修記錄" sheetId="2" r:id="rId2"/>
-    <sheet name="料號對照" sheetId="3" r:id="rId3"/>
-    <sheet name="系品彙總" sheetId="4" r:id="rId4"/>
-    <sheet name="說明" sheetId="5" r:id="rId5"/>
+    <sheet name="本月彙總" sheetId="3" r:id="rId3"/>
+    <sheet name="料號對照" sheetId="4" r:id="rId4"/>
+    <sheet name="系品彙總" sheetId="5" r:id="rId5"/>
+    <sheet name="說明" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -8846,6 +8847,2819 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F180"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>【本月彙總】公式自動計算，填寫資料後立即顯示 — 無需手動更新</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>本月維修總筆數</v>
+      </c>
+      <c r="B3">
+        <f>COUNTA(維修記錄!$D$4:$D$503)</f>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>本月報廢件數</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>報廢率</v>
+      </c>
+      <c r="B5">
+        <f>IFERROR(COUNTIF(維修記錄!$W$4:$W$503,"Y")/COUNTA(維修記錄!$D$4:$D$503),"—")</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>NTF件數（無法重現）</v>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(維修記錄!$L$4:$L$503,"NTF*")</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>NTF比率</v>
+      </c>
+      <c r="B7">
+        <f>IFERROR(COUNTIF(維修記錄!$L$4:$L$503,"NTF*")/COUNTA(維修記錄!$D$4:$D$503),"—")</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>▌ 各品號故障彙總</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>器材品號</v>
+      </c>
+      <c r="B10" t="str">
+        <v>大類</v>
+      </c>
+      <c r="C10" t="str">
+        <v>故障件數</v>
+      </c>
+      <c r="D10" t="str">
+        <v>報廢件數</v>
+      </c>
+      <c r="E10" t="str">
+        <v>報廢率</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ADR3A08</v>
+      </c>
+      <c r="B11" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A11)</f>
+      </c>
+      <c r="D11">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A11,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E11">
+        <f>IFERROR(D11/C11,"")</f>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ADR3A16</v>
+      </c>
+      <c r="B12" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A12)</f>
+      </c>
+      <c r="D12">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A12,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E12">
+        <f>IFERROR(D12/C12,"")</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AH13A36</v>
+      </c>
+      <c r="B13" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A13)</f>
+      </c>
+      <c r="D13">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A13,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E13">
+        <f>IFERROR(D13/C13,"")</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AH13B3Z</v>
+      </c>
+      <c r="B14" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A14)</f>
+      </c>
+      <c r="D14">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A14,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E14">
+        <f>IFERROR(D14/C14,"")</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AH13C36</v>
+      </c>
+      <c r="B15" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A15)</f>
+      </c>
+      <c r="D15">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A15,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E15">
+        <f>IFERROR(D15/C15,"")</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AH43B3Z</v>
+      </c>
+      <c r="B16" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A16)</f>
+      </c>
+      <c r="D16">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A16,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E16">
+        <f>IFERROR(D16/C16,"")</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AH83A28</v>
+      </c>
+      <c r="B17" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A17)</f>
+      </c>
+      <c r="D17">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A17,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E17">
+        <f>IFERROR(D17/C17,"")</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AH83B3Z</v>
+      </c>
+      <c r="B18" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A18)</f>
+      </c>
+      <c r="D18">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A18,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E18">
+        <f>IFERROR(D18/C18,"")</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AH83D28</v>
+      </c>
+      <c r="B19" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A19)</f>
+      </c>
+      <c r="D19">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A19,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E19">
+        <f>IFERROR(D19/C19,"")</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AH83D3Z</v>
+      </c>
+      <c r="B20" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A20)</f>
+      </c>
+      <c r="D20">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A20,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E20">
+        <f>IFERROR(D20/C20,"")</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>APCB</v>
+      </c>
+      <c r="B21" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A21)</f>
+      </c>
+      <c r="D21">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A21,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E21">
+        <f>IFERROR(D21/C21,"")</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AW53B3Z</v>
+      </c>
+      <c r="B22" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C22">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A22)</f>
+      </c>
+      <c r="D22">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A22,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E22">
+        <f>IFERROR(D22/C22,"")</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HU316PE</v>
+      </c>
+      <c r="B23" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C23">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A23)</f>
+      </c>
+      <c r="D23">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A23,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E23">
+        <f>IFERROR(D23/C23,"")</f>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HU382PE</v>
+      </c>
+      <c r="B24" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A24)</f>
+      </c>
+      <c r="D24">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A24,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E24">
+        <f>IFERROR(D24/C24,"")</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>IP43A3Z</v>
+      </c>
+      <c r="B25" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C25">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A25)</f>
+      </c>
+      <c r="D25">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A25,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E25">
+        <f>IFERROR(D25/C25,"")</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>IP43B3Z</v>
+      </c>
+      <c r="B26" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C26">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A26)</f>
+      </c>
+      <c r="D26">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A26,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E26">
+        <f>IFERROR(D26/C26,"")</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>IP43C28</v>
+      </c>
+      <c r="B27" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C27">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A27)</f>
+      </c>
+      <c r="D27">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A27,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E27">
+        <f>IFERROR(D27/C27,"")</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>IP43D28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C28">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A28)</f>
+      </c>
+      <c r="D28">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A28,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E28">
+        <f>IFERROR(D28/C28,"")</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>IP43L08</v>
+      </c>
+      <c r="B29" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C29">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A29)</f>
+      </c>
+      <c r="D29">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A29,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E29">
+        <f>IFERROR(D29/C29,"")</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>IP53C21</v>
+      </c>
+      <c r="B30" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C30">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A30)</f>
+      </c>
+      <c r="D30">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A30,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E30">
+        <f>IFERROR(D30/C30,"")</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>IP83B3Z</v>
+      </c>
+      <c r="B31" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C31">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A31)</f>
+      </c>
+      <c r="D31">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A31,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E31">
+        <f>IFERROR(D31/C31,"")</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>IPC3A36</v>
+      </c>
+      <c r="B32" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C32">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A32)</f>
+      </c>
+      <c r="D32">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A32,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E32">
+        <f>IFERROR(D32/C32,"")</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>IPC3A3Z</v>
+      </c>
+      <c r="B33" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C33">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A33)</f>
+      </c>
+      <c r="D33">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A33,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E33">
+        <f>IFERROR(D33/C33,"")</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>IPC3S2W</v>
+      </c>
+      <c r="B34" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C34">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A34)</f>
+      </c>
+      <c r="D34">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A34,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E34">
+        <f>IFERROR(D34/C34,"")</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>IPD3F16</v>
+      </c>
+      <c r="B35" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C35">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A35)</f>
+      </c>
+      <c r="D35">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A35,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E35">
+        <f>IFERROR(D35/C35,"")</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LPR3B32</v>
+      </c>
+      <c r="B36" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C36">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A36)</f>
+      </c>
+      <c r="D36">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A36,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E36">
+        <f>IFERROR(D36/C36,"")</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>LPR3B3Z</v>
+      </c>
+      <c r="B37" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C37">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A37)</f>
+      </c>
+      <c r="D37">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A37,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E37">
+        <f>IFERROR(D37/C37,"")</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>NVR3F08</v>
+      </c>
+      <c r="B38" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C38">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A38)</f>
+      </c>
+      <c r="D38">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A38,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E38">
+        <f>IFERROR(D38/C38,"")</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>NVR3G16</v>
+      </c>
+      <c r="B39" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C39">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A39)</f>
+      </c>
+      <c r="D39">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A39,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E39">
+        <f>IFERROR(D39/C39,"")</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>NVR3G32</v>
+      </c>
+      <c r="B40" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C40">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A40)</f>
+      </c>
+      <c r="D40">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A40,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E40">
+        <f>IFERROR(D40/C40,"")</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>NVR3H16</v>
+      </c>
+      <c r="B41" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C41">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A41)</f>
+      </c>
+      <c r="D41">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A41,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E41">
+        <f>IFERROR(D41/C41,"")</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>NVR3I08</v>
+      </c>
+      <c r="B42" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C42">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A42)</f>
+      </c>
+      <c r="D42">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A42,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E42">
+        <f>IFERROR(D42/C42,"")</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>POEEXP1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C43">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A43)</f>
+      </c>
+      <c r="D43">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A43,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E43">
+        <f>IFERROR(D43/C43,"")</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TDB633A</v>
+      </c>
+      <c r="B44" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C44">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A44)</f>
+      </c>
+      <c r="D44">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A44,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E44">
+        <f>IFERROR(D44/C44,"")</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>VD43A16</v>
+      </c>
+      <c r="B45" t="str">
+        <v>監視器</v>
+      </c>
+      <c r="C45">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A45)</f>
+      </c>
+      <c r="D45">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A45,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E45">
+        <f>IFERROR(D45/C45,"")</f>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CDRT010</v>
+      </c>
+      <c r="B46" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C46">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A46)</f>
+      </c>
+      <c r="D46">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A46,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E46">
+        <f>IFERROR(D46/C46,"")</f>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CDRT030</v>
+      </c>
+      <c r="B47" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C47">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A47)</f>
+      </c>
+      <c r="D47">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A47,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E47">
+        <f>IFERROR(D47/C47,"")</f>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CDRT080</v>
+      </c>
+      <c r="B48" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C48">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A48)</f>
+      </c>
+      <c r="D48">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A48,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E48">
+        <f>IFERROR(D48/C48,"")</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CRS0020</v>
+      </c>
+      <c r="B49" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C49">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A49)</f>
+      </c>
+      <c r="D49">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A49,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E49">
+        <f>IFERROR(D49/C49,"")</f>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CTM0051</v>
+      </c>
+      <c r="B50" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C50">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A50)</f>
+      </c>
+      <c r="D50">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A50,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E50">
+        <f>IFERROR(D50/C50,"")</f>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CTMS020</v>
+      </c>
+      <c r="B51" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C51">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A51)</f>
+      </c>
+      <c r="D51">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A51,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E51">
+        <f>IFERROR(D51/C51,"")</f>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CTO0010</v>
+      </c>
+      <c r="B52" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C52">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A52)</f>
+      </c>
+      <c r="D52">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A52,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E52">
+        <f>IFERROR(D52/C52,"")</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>CTO0020</v>
+      </c>
+      <c r="B53" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C53">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A53)</f>
+      </c>
+      <c r="D53">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A53,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E53">
+        <f>IFERROR(D53/C53,"")</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>CTO0030</v>
+      </c>
+      <c r="B54" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C54">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A54)</f>
+      </c>
+      <c r="D54">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A54,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E54">
+        <f>IFERROR(D54/C54,"")</f>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>EPES010</v>
+      </c>
+      <c r="B55" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C55">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A55)</f>
+      </c>
+      <c r="D55">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A55,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E55">
+        <f>IFERROR(D55/C55,"")</f>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>NTS001A</v>
+      </c>
+      <c r="B56" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C56">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A56)</f>
+      </c>
+      <c r="D56">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A56,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E56">
+        <f>IFERROR(D56/C56,"")</f>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>NTS0060</v>
+      </c>
+      <c r="B57" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C57">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A57)</f>
+      </c>
+      <c r="D57">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A57,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E57">
+        <f>IFERROR(D57/C57,"")</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>OPI3010</v>
+      </c>
+      <c r="B58" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C58">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A58)</f>
+      </c>
+      <c r="D58">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A58,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E58">
+        <f>IFERROR(D58/C58,"")</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>OPT0030</v>
+      </c>
+      <c r="B59" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C59">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A59)</f>
+      </c>
+      <c r="D59">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A59,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E59">
+        <f>IFERROR(D59/C59,"")</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>PCAS600</v>
+      </c>
+      <c r="B60" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C60">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A60)</f>
+      </c>
+      <c r="D60">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A60,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E60">
+        <f>IFERROR(D60/C60,"")</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>RFSD020</v>
+      </c>
+      <c r="B61" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C61">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A61)</f>
+      </c>
+      <c r="D61">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A61,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E61">
+        <f>IFERROR(D61/C61,"")</f>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>SCA0020</v>
+      </c>
+      <c r="B62" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C62">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A62)</f>
+      </c>
+      <c r="D62">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A62,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E62">
+        <f>IFERROR(D62/C62,"")</f>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>SCL0020</v>
+      </c>
+      <c r="B63" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C63">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A63)</f>
+      </c>
+      <c r="D63">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A63,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E63">
+        <f>IFERROR(D63/C63,"")</f>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>SCX0050</v>
+      </c>
+      <c r="B64" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C64">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A64)</f>
+      </c>
+      <c r="D64">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A64,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E64">
+        <f>IFERROR(D64/C64,"")</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SCX0051</v>
+      </c>
+      <c r="B65" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C65">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A65)</f>
+      </c>
+      <c r="D65">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A65,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E65">
+        <f>IFERROR(D65/C65,"")</f>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SCX051A</v>
+      </c>
+      <c r="B66" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C66">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A66)</f>
+      </c>
+      <c r="D66">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A66,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E66">
+        <f>IFERROR(D66/C66,"")</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SHT0071</v>
+      </c>
+      <c r="B67" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C67">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A67)</f>
+      </c>
+      <c r="D67">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A67,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E67">
+        <f>IFERROR(D67/C67,"")</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SHT0072</v>
+      </c>
+      <c r="B68" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C68">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A68)</f>
+      </c>
+      <c r="D68">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A68,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E68">
+        <f>IFERROR(D68/C68,"")</f>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SHT0081</v>
+      </c>
+      <c r="B69" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C69">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A69)</f>
+      </c>
+      <c r="D69">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A69,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E69">
+        <f>IFERROR(D69/C69,"")</f>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SPC0010</v>
+      </c>
+      <c r="B70" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C70">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A70)</f>
+      </c>
+      <c r="D70">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A70,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E70">
+        <f>IFERROR(D70/C70,"")</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SPK009B</v>
+      </c>
+      <c r="B71" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C71">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A71)</f>
+      </c>
+      <c r="D71">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A71,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E71">
+        <f>IFERROR(D71/C71,"")</f>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SPK011A</v>
+      </c>
+      <c r="B72" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C72">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A72)</f>
+      </c>
+      <c r="D72">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A72,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E72">
+        <f>IFERROR(D72/C72,"")</f>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>SPM0051</v>
+      </c>
+      <c r="B73" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C73">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A73)</f>
+      </c>
+      <c r="D73">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A73,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E73">
+        <f>IFERROR(D73/C73,"")</f>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>SPM0171</v>
+      </c>
+      <c r="B74" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C74">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A74)</f>
+      </c>
+      <c r="D74">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A74,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E74">
+        <f>IFERROR(D74/C74,"")</f>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>SVAT500</v>
+      </c>
+      <c r="B75" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C75">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A75)</f>
+      </c>
+      <c r="D75">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A75,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E75">
+        <f>IFERROR(D75/C75,"")</f>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TCNT010</v>
+      </c>
+      <c r="B76" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C76">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A76)</f>
+      </c>
+      <c r="D76">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A76,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E76">
+        <f>IFERROR(D76/C76,"")</f>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TCNT030</v>
+      </c>
+      <c r="B77" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C77">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A77)</f>
+      </c>
+      <c r="D77">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A77,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E77">
+        <f>IFERROR(D77/C77,"")</f>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TCNT03D</v>
+      </c>
+      <c r="B78" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C78">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A78)</f>
+      </c>
+      <c r="D78">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A78,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E78">
+        <f>IFERROR(D78/C78,"")</f>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TFM0020</v>
+      </c>
+      <c r="B79" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C79">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A79)</f>
+      </c>
+      <c r="D79">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A79,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E79">
+        <f>IFERROR(D79/C79,"")</f>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>THS0010</v>
+      </c>
+      <c r="B80" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C80">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A80)</f>
+      </c>
+      <c r="D80">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A80,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E80">
+        <f>IFERROR(D80/C80,"")</f>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>THS001A</v>
+      </c>
+      <c r="B81" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C81">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A81)</f>
+      </c>
+      <c r="D81">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A81,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E81">
+        <f>IFERROR(D81/C81,"")</f>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>THS0020</v>
+      </c>
+      <c r="B82" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C82">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A82)</f>
+      </c>
+      <c r="D82">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A82,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E82">
+        <f>IFERROR(D82/C82,"")</f>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>THS0030</v>
+      </c>
+      <c r="B83" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C83">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A83)</f>
+      </c>
+      <c r="D83">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A83,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E83">
+        <f>IFERROR(D83/C83,"")</f>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>THSM010</v>
+      </c>
+      <c r="B84" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C84">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A84)</f>
+      </c>
+      <c r="D84">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A84,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E84">
+        <f>IFERROR(D84/C84,"")</f>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TLED010</v>
+      </c>
+      <c r="B85" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C85">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A85)</f>
+      </c>
+      <c r="D85">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A85,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E85">
+        <f>IFERROR(D85/C85,"")</f>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TPAD050</v>
+      </c>
+      <c r="B86" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C86">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A86)</f>
+      </c>
+      <c r="D86">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A86,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E86">
+        <f>IFERROR(D86/C86,"")</f>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TPW0010</v>
+      </c>
+      <c r="B87" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C87">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A87)</f>
+      </c>
+      <c r="D87">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A87,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E87">
+        <f>IFERROR(D87/C87,"")</f>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TPW0050</v>
+      </c>
+      <c r="B88" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C88">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A88)</f>
+      </c>
+      <c r="D88">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A88,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E88">
+        <f>IFERROR(D88/C88,"")</f>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TSM0030</v>
+      </c>
+      <c r="B89" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C89">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A89)</f>
+      </c>
+      <c r="D89">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A89,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E89">
+        <f>IFERROR(D89/C89,"")</f>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>VTS0010</v>
+      </c>
+      <c r="B90" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C90">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A90)</f>
+      </c>
+      <c r="D90">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A90,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E90">
+        <f>IFERROR(D90/C90,"")</f>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>XRCS-S1</v>
+      </c>
+      <c r="B91" t="str">
+        <v>傳統保全</v>
+      </c>
+      <c r="C91">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A91)</f>
+      </c>
+      <c r="D91">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A91,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E91">
+        <f>IFERROR(D91/C91,"")</f>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>IOT0600</v>
+      </c>
+      <c r="B92" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C92">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A92)</f>
+      </c>
+      <c r="D92">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A92,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E92">
+        <f>IFERROR(D92/C92,"")</f>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>IOT0700</v>
+      </c>
+      <c r="B93" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C93">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A93)</f>
+      </c>
+      <c r="D93">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A93,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E93">
+        <f>IFERROR(D93/C93,"")</f>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>IOT0800</v>
+      </c>
+      <c r="B94" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C94">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A94)</f>
+      </c>
+      <c r="D94">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A94,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E94">
+        <f>IFERROR(D94/C94,"")</f>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>IRL32ZB</v>
+      </c>
+      <c r="B95" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C95">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A95)</f>
+      </c>
+      <c r="D95">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A95,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E95">
+        <f>IFERROR(D95/C95,"")</f>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>KDSL7ZB</v>
+      </c>
+      <c r="B96" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C96">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A96)</f>
+      </c>
+      <c r="D96">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A96,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E96">
+        <f>IFERROR(D96/C96,"")</f>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>RFAS010</v>
+      </c>
+      <c r="B97" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C97">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A97)</f>
+      </c>
+      <c r="D97">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A97,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E97">
+        <f>IFERROR(D97/C97,"")</f>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>RFDIO10</v>
+      </c>
+      <c r="B98" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C98">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A98)</f>
+      </c>
+      <c r="D98">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A98,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E98">
+        <f>IFERROR(D98/C98,"")</f>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>RFPIR30</v>
+      </c>
+      <c r="B99" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C99">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A99)</f>
+      </c>
+      <c r="D99">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A99,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E99">
+        <f>IFERROR(D99/C99,"")</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>RFRT030</v>
+      </c>
+      <c r="B100" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C100">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A100)</f>
+      </c>
+      <c r="D100">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A100,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E100">
+        <f>IFERROR(D100/C100,"")</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>RFSPC10</v>
+      </c>
+      <c r="B101" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C101">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A101)</f>
+      </c>
+      <c r="D101">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A101,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E101">
+        <f>IFERROR(D101/C101,"")</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>RFSPM21</v>
+      </c>
+      <c r="B102" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C102">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A102)</f>
+      </c>
+      <c r="D102">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A102,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E102">
+        <f>IFERROR(D102/C102,"")</f>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>RFSSL20</v>
+      </c>
+      <c r="B103" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C103">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A103)</f>
+      </c>
+      <c r="D103">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A103,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E103">
+        <f>IFERROR(D103/C103,"")</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>RFTG030</v>
+      </c>
+      <c r="B104" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C104">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A104)</f>
+      </c>
+      <c r="D104">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A104,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E104">
+        <f>IFERROR(D104/C104,"")</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>RFTM010</v>
+      </c>
+      <c r="B105" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C105">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A105)</f>
+      </c>
+      <c r="D105">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A105,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E105">
+        <f>IFERROR(D105/C105,"")</f>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>RFVX41T</v>
+      </c>
+      <c r="B106" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C106">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A106)</f>
+      </c>
+      <c r="D106">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A106,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E106">
+        <f>IFERROR(D106/C106,"")</f>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>RF11940</v>
+      </c>
+      <c r="B107" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C107">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A107)</f>
+      </c>
+      <c r="D107">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A107,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E107">
+        <f>IFERROR(D107/C107,"")</f>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>RL320ZB</v>
+      </c>
+      <c r="B108" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C108">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A108)</f>
+      </c>
+      <c r="D108">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A108,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E108">
+        <f>IFERROR(D108/C108,"")</f>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>RSPM031</v>
+      </c>
+      <c r="B109" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C109">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A109)</f>
+      </c>
+      <c r="D109">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A109,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E109">
+        <f>IFERROR(D109/C109,"")</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>RSPMB21</v>
+      </c>
+      <c r="B110" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C110">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A110)</f>
+      </c>
+      <c r="D110">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A110,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E110">
+        <f>IFERROR(D110/C110,"")</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TPS0050</v>
+      </c>
+      <c r="B111" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C111">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A111)</f>
+      </c>
+      <c r="D111">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A111,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E111">
+        <f>IFERROR(D111/C111,"")</f>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TPS041A</v>
+      </c>
+      <c r="B112" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C112">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A112)</f>
+      </c>
+      <c r="D112">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A112,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E112">
+        <f>IFERROR(D112/C112,"")</f>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TPSZB41</v>
+      </c>
+      <c r="B113" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C113">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A113)</f>
+      </c>
+      <c r="D113">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A113,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E113">
+        <f>IFERROR(D113/C113,"")</f>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TRANS12</v>
+      </c>
+      <c r="B114" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C114">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A114)</f>
+      </c>
+      <c r="D114">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A114,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E114">
+        <f>IFERROR(D114/C114,"")</f>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>XRCSS1</v>
+      </c>
+      <c r="B115" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C115">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A115)</f>
+      </c>
+      <c r="D115">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A115,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E115">
+        <f>IFERROR(D115/C115,"")</f>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>ZBACI20</v>
+      </c>
+      <c r="B116" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C116">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A116)</f>
+      </c>
+      <c r="D116">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A116,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E116">
+        <f>IFERROR(D116/C116,"")</f>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>ZBDIO80</v>
+      </c>
+      <c r="B117" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C117">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A117)</f>
+      </c>
+      <c r="D117">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A117,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E117">
+        <f>IFERROR(D117/C117,"")</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>ZBDIO90</v>
+      </c>
+      <c r="B118" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C118">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A118)</f>
+      </c>
+      <c r="D118">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A118,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E118">
+        <f>IFERROR(D118/C118,"")</f>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>ZBHD060</v>
+      </c>
+      <c r="B119" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C119">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A119)</f>
+      </c>
+      <c r="D119">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A119,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E119">
+        <f>IFERROR(D119/C119,"")</f>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>ZBIRC50</v>
+      </c>
+      <c r="B120" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C120">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A120)</f>
+      </c>
+      <c r="D120">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A120,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E120">
+        <f>IFERROR(D120/C120,"")</f>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>ZBIRC5S</v>
+      </c>
+      <c r="B121" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C121">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A121)</f>
+      </c>
+      <c r="D121">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A121,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E121">
+        <f>IFERROR(D121/C121,"")</f>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>ZBPIR50</v>
+      </c>
+      <c r="B122" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C122">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A122)</f>
+      </c>
+      <c r="D122">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A122,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E122">
+        <f>IFERROR(D122/C122,"")</f>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>ZBPIR5P</v>
+      </c>
+      <c r="B123" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C123">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A123)</f>
+      </c>
+      <c r="D123">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A123,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E123">
+        <f>IFERROR(D123/C123,"")</f>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>ZBRT050</v>
+      </c>
+      <c r="B124" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C124">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A124)</f>
+      </c>
+      <c r="D124">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A124,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E124">
+        <f>IFERROR(D124/C124,"")</f>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>ZBSD060</v>
+      </c>
+      <c r="B125" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C125">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A125)</f>
+      </c>
+      <c r="D125">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A125,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E125">
+        <f>IFERROR(D125/C125,"")</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>ZBSPC40</v>
+      </c>
+      <c r="B126" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C126">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A126)</f>
+      </c>
+      <c r="D126">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A126,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E126">
+        <f>IFERROR(D126/C126,"")</f>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>ZBSSL30</v>
+      </c>
+      <c r="B127" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C127">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A127)</f>
+      </c>
+      <c r="D127">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A127,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E127">
+        <f>IFERROR(D127/C127,"")</f>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>ZBTG030</v>
+      </c>
+      <c r="B128" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C128">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A128)</f>
+      </c>
+      <c r="D128">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A128,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E128">
+        <f>IFERROR(D128/C128,"")</f>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>ZBVOS10</v>
+      </c>
+      <c r="B129" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C129">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A129)</f>
+      </c>
+      <c r="D129">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A129,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E129">
+        <f>IFERROR(D129/C129,"")</f>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>ZBVX41T</v>
+      </c>
+      <c r="B130" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C130">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A130)</f>
+      </c>
+      <c r="D130">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A130,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E130">
+        <f>IFERROR(D130/C130,"")</f>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>ZBWD199</v>
+      </c>
+      <c r="B131" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C131">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A131)</f>
+      </c>
+      <c r="D131">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A131,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E131">
+        <f>IFERROR(D131/C131,"")</f>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>ZBWSS20</v>
+      </c>
+      <c r="B132" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C132">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A132)</f>
+      </c>
+      <c r="D132">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A132,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E132">
+        <f>IFERROR(D132/C132,"")</f>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>ZCT80VA</v>
+      </c>
+      <c r="B133" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C133">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A133)</f>
+      </c>
+      <c r="D133">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A133,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E133">
+        <f>IFERROR(D133/C133,"")</f>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ZCTE10A</v>
+      </c>
+      <c r="B134" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C134">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A134)</f>
+      </c>
+      <c r="D134">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A134,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E134">
+        <f>IFERROR(D134/C134,"")</f>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>ZCTE20A</v>
+      </c>
+      <c r="B135" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C135">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A135)</f>
+      </c>
+      <c r="D135">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A135,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E135">
+        <f>IFERROR(D135/C135,"")</f>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>ZSPMB31</v>
+      </c>
+      <c r="B136" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C136">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A136)</f>
+      </c>
+      <c r="D136">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A136,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E136">
+        <f>IFERROR(D136/C136,"")</f>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>ZSPMB51</v>
+      </c>
+      <c r="B137" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C137">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A137)</f>
+      </c>
+      <c r="D137">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A137,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E137">
+        <f>IFERROR(D137/C137,"")</f>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>ZSPMG22</v>
+      </c>
+      <c r="B138" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C138">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A138)</f>
+      </c>
+      <c r="D138">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A138,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E138">
+        <f>IFERROR(D138/C138,"")</f>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>ZSPMG31</v>
+      </c>
+      <c r="B139" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C139">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A139)</f>
+      </c>
+      <c r="D139">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A139,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E139">
+        <f>IFERROR(D139/C139,"")</f>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>ZSPMG51</v>
+      </c>
+      <c r="B140" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C140">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A140)</f>
+      </c>
+      <c r="D140">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A140,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E140">
+        <f>IFERROR(D140/C140,"")</f>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>ZWDIO20</v>
+      </c>
+      <c r="B141" t="str">
+        <v>無線保全</v>
+      </c>
+      <c r="C141">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A141)</f>
+      </c>
+      <c r="D141">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A141,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E141">
+        <f>IFERROR(D141/C141,"")</f>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>MS0M043</v>
+      </c>
+      <c r="B142" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C142">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A142)</f>
+      </c>
+      <c r="D142">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A142,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E142">
+        <f>IFERROR(D142/C142,"")</f>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>MSM0801</v>
+      </c>
+      <c r="B143" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C143">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A143)</f>
+      </c>
+      <c r="D143">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A143,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E143">
+        <f>IFERROR(D143/C143,"")</f>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>MSM0810</v>
+      </c>
+      <c r="B144" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C144">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A144)</f>
+      </c>
+      <c r="D144">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A144,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E144">
+        <f>IFERROR(D144/C144,"")</f>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>MSM1201</v>
+      </c>
+      <c r="B145" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C145">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A145)</f>
+      </c>
+      <c r="D145">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A145,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E145">
+        <f>IFERROR(D145/C145,"")</f>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>MSM1301</v>
+      </c>
+      <c r="B146" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C146">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A146)</f>
+      </c>
+      <c r="D146">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A146,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E146">
+        <f>IFERROR(D146/C146,"")</f>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>MSV0201</v>
+      </c>
+      <c r="B147" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C147">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A147)</f>
+      </c>
+      <c r="D147">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A147,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E147">
+        <f>IFERROR(D147/C147,"")</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>MSV0402</v>
+      </c>
+      <c r="B148" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C148">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A148)</f>
+      </c>
+      <c r="D148">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A148,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E148">
+        <f>IFERROR(D148/C148,"")</f>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>MSV0502</v>
+      </c>
+      <c r="B149" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C149">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A149)</f>
+      </c>
+      <c r="D149">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A149,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E149">
+        <f>IFERROR(D149/C149,"")</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TPS0041</v>
+      </c>
+      <c r="B150" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C150">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A150)</f>
+      </c>
+      <c r="D150">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A150,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E150">
+        <f>IFERROR(D150/C150,"")</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TPS0061</v>
+      </c>
+      <c r="B151" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C151">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A151)</f>
+      </c>
+      <c r="D151">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A151,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E151">
+        <f>IFERROR(D151/C151,"")</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TPS0071</v>
+      </c>
+      <c r="B152" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C152">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A152)</f>
+      </c>
+      <c r="D152">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A152,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E152">
+        <f>IFERROR(D152/C152,"")</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TPAD054</v>
+      </c>
+      <c r="B153" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C153">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A153)</f>
+      </c>
+      <c r="D153">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A153,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E153">
+        <f>IFERROR(D153/C153,"")</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TPAD055</v>
+      </c>
+      <c r="B154" t="str">
+        <v>車機系統</v>
+      </c>
+      <c r="C154">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A154)</f>
+      </c>
+      <c r="D154">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A154,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E154">
+        <f>IFERROR(D154/C154,"")</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>AED0501</v>
+      </c>
+      <c r="B155" t="str">
+        <v>AED</v>
+      </c>
+      <c r="C155">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A155)</f>
+      </c>
+      <c r="D155">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A155,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E155">
+        <f>IFERROR(D155/C155,"")</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>AED4G10</v>
+      </c>
+      <c r="B156" t="str">
+        <v>AED</v>
+      </c>
+      <c r="C156">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A156)</f>
+      </c>
+      <c r="D156">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A156,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E156">
+        <f>IFERROR(D156/C156,"")</f>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>AED4G20</v>
+      </c>
+      <c r="B157" t="str">
+        <v>AED</v>
+      </c>
+      <c r="C157">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A157)</f>
+      </c>
+      <c r="D157">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A157,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E157">
+        <f>IFERROR(D157/C157,"")</f>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>AED4G30</v>
+      </c>
+      <c r="B158" t="str">
+        <v>AED</v>
+      </c>
+      <c r="C158">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A158)</f>
+      </c>
+      <c r="D158">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A158,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E158">
+        <f>IFERROR(D158/C158,"")</f>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>AED4G40</v>
+      </c>
+      <c r="B159" t="str">
+        <v>AED</v>
+      </c>
+      <c r="C159">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A159)</f>
+      </c>
+      <c r="D159">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A159,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E159">
+        <f>IFERROR(D159/C159,"")</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>OPC002C</v>
+      </c>
+      <c r="B160" t="str">
+        <v>門禁</v>
+      </c>
+      <c r="C160">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A160)</f>
+      </c>
+      <c r="D160">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A160,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E160">
+        <f>IFERROR(D160/C160,"")</f>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>OPC003C</v>
+      </c>
+      <c r="B161" t="str">
+        <v>門禁</v>
+      </c>
+      <c r="C161">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A161)</f>
+      </c>
+      <c r="D161">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A161,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E161">
+        <f>IFERROR(D161/C161,"")</f>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>OPC0050</v>
+      </c>
+      <c r="B162" t="str">
+        <v>門禁</v>
+      </c>
+      <c r="C162">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A162)</f>
+      </c>
+      <c r="D162">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A162,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E162">
+        <f>IFERROR(D162/C162,"")</f>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>OPC1050</v>
+      </c>
+      <c r="B163" t="str">
+        <v>門禁</v>
+      </c>
+      <c r="C163">
+        <f>COUNTIF(維修記錄!$C$4:$C$503,A163)</f>
+      </c>
+      <c r="D163">
+        <f>COUNTIFS(維修記錄!$C$4:$C$503,A163,維修記錄!$W$4:$W$503,"Y")</f>
+      </c>
+      <c r="E163">
+        <f>IFERROR(D163/C163,"")</f>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>▌ 故障原因大類分布</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>故障原因</v>
+      </c>
+      <c r="B167" t="str">
+        <v>件數</v>
+      </c>
+      <c r="C167" t="str">
+        <v>佔比</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>電源系統</v>
+      </c>
+      <c r="B168">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A168)</f>
+      </c>
+      <c r="C168">
+        <f>IFERROR(B168/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>主板PCB</v>
+      </c>
+      <c r="B169">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A169)</f>
+      </c>
+      <c r="C169">
+        <f>IFERROR(B169/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>顯示螢幕</v>
+      </c>
+      <c r="B170">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A170)</f>
+      </c>
+      <c r="C170">
+        <f>IFERROR(B170/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>儲存記憶</v>
+      </c>
+      <c r="B171">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A171)</f>
+      </c>
+      <c r="C171">
+        <f>IFERROR(B171/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>感測鏡頭</v>
+      </c>
+      <c r="B172">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A172)</f>
+      </c>
+      <c r="C172">
+        <f>IFERROR(B172/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>機構外觀</v>
+      </c>
+      <c r="B173">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A173)</f>
+      </c>
+      <c r="C173">
+        <f>IFERROR(B173/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>通訊網路</v>
+      </c>
+      <c r="B174">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A174)</f>
+      </c>
+      <c r="C174">
+        <f>IFERROR(B174/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>韌體軟體</v>
+      </c>
+      <c r="B175">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A175)</f>
+      </c>
+      <c r="C175">
+        <f>IFERROR(B175/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>運輸損傷</v>
+      </c>
+      <c r="B176">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A176)</f>
+      </c>
+      <c r="C176">
+        <f>IFERROR(B176/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>電磁靜電</v>
+      </c>
+      <c r="B177">
+        <f>COUNTIF(維修記錄!$J$4:$J$503,A177)</f>
+      </c>
+      <c r="C177">
+        <f>IFERROR(B177/COUNTA(維修記錄!$D$4:$D$503),"")</f>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F180"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C111"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
@@ -9331,7 +12145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D26"/>
   <cols>
@@ -9432,7 +12246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A44"/>
   <cols>
